--- a/CodeSystem-stroke-discharge-summary-section-cs.xlsx
+++ b/CodeSystem-stroke-discharge-summary-section-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-discharge-summary-section-cs.xlsx
+++ b/CodeSystem-stroke-discharge-summary-section-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/stroke-discharge-summary-section-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/stroke-discharge-summary-section-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://tecnomod-um.org/CodeSystem/stroke-discharge-summary-section-cs.</t>
+    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://qualityregistry.org/CodeSystem/stroke-discharge-summary-section-cs.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-stroke-discharge-summary-section-cs.xlsx
+++ b/CodeSystem-stroke-discharge-summary-section-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-discharge-summary-section-cs.xlsx
+++ b/CodeSystem-stroke-discharge-summary-section-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-discharge-summary-section-cs.xlsx
+++ b/CodeSystem-stroke-discharge-summary-section-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
